--- a/outputs/report_database.xlsx
+++ b/outputs/report_database.xlsx
@@ -588,6 +588,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -650,6 +651,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -709,14 +711,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>dailyCost number corrected; cumulativeCost number corrected</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -779,6 +777,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -838,7 +837,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>mudType missing; mudDensity missing</t>
         </is>
       </c>
     </row>
@@ -970,6 +974,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1029,7 +1034,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>mudType missing; mudDensity missing</t>
         </is>
       </c>
     </row>
@@ -1094,6 +1104,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1156,6 +1167,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1218,6 +1230,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1280,6 +1293,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1344,7 +1358,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>operation hours total 8.00</t>
+          <t>mudType missing; mudDensity missing; operation hours total 8.00</t>
         </is>
       </c>
     </row>
@@ -1409,6 +1423,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1471,6 +1486,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1533,6 +1549,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1592,7 +1609,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>mudType missing; mudDensity missing</t>
         </is>
       </c>
     </row>
@@ -1657,6 +1679,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1716,7 +1739,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>mudType missing; mudDensity missing</t>
         </is>
       </c>
     </row>
@@ -1781,6 +1809,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1843,6 +1872,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1905,6 +1935,7 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1964,7 +1995,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>mudType missing; mudDensity missing</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2067,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected; operation hours total 19.00</t>
+          <t>operation hours total 19.00</t>
         </is>
       </c>
     </row>
@@ -2093,14 +2129,10 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2160,14 +2192,10 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2227,14 +2255,10 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2294,14 +2318,10 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2361,14 +2381,10 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2428,14 +2444,10 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2495,14 +2507,10 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2562,14 +2570,10 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2629,14 +2633,10 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2696,14 +2696,10 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2763,14 +2759,10 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2830,14 +2822,10 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2902,7 +2890,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>dailyCost number corrected; afeCost number corrected; cumulativeCost number corrected; perforation_intervals row 1 date is in the future</t>
+          <t>perforation_intervals row 1 date is in the future</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4504,6 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -37948,7 +37935,6 @@
           <t>HENRY JIMENEZ</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
           <t>107</t>

--- a/outputs/report_database.xlsx
+++ b/outputs/report_database.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -458,6 +458,11 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,6 +531,31 @@
           <t>validation_warnings</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>confirmation_status</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>confirmed_at</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>confirmed_by</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>confirmation_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -588,7 +618,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -651,7 +680,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -714,7 +742,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -777,7 +804,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -827,7 +853,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:00+00:00</t>
+          <t>2026-07-04T13:21:31+00:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -845,6 +871,12 @@
           <t>mudType missing; mudDensity missing</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -961,7 +993,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:01+00:00</t>
+          <t>2026-07-04T13:21:31+00:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -974,7 +1006,12 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1091,7 +1128,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:01+00:00</t>
+          <t>2026-07-04T13:21:31+00:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1104,7 +1141,12 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1167,7 +1209,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1230,7 +1271,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1293,7 +1333,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1423,7 +1462,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1486,7 +1524,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1549,7 +1586,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1599,7 +1635,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:04+00:00</t>
+          <t>2026-07-04T13:21:31+00:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1617,6 +1653,12 @@
           <t>mudType missing; mudDensity missing</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1679,7 +1721,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1809,7 +1850,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1872,7 +1912,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1922,7 +1961,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:06+00:00</t>
+          <t>2026-07-04T13:21:31+00:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1935,7 +1974,12 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2132,7 +2176,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2195,7 +2238,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2258,7 +2300,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2321,7 +2362,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2384,7 +2424,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2447,7 +2486,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2510,7 +2548,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2573,7 +2610,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2636,7 +2672,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2699,7 +2734,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2762,7 +2796,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2825,7 +2858,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4802,7 +4834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -4814,6 +4846,8 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4860,6 +4894,16 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>operation_details</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>system_op_type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>confirmed_op_type</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -11736,6 +11780,8 @@
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11782,6 +11828,16 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>operation_details</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>system_op_type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>confirmed_op_type</t>
         </is>
       </c>
     </row>
@@ -24163,7 +24219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I191"/>
+  <dimension ref="A1:K191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -24175,6 +24231,8 @@
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24221,6 +24279,16 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>operation_details</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>system_op_type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>confirmed_op_type</t>
         </is>
       </c>
     </row>
@@ -25283,6 +25351,16 @@
 PILDORA SELLANTE DE 9.6 PPG X 40 SQT @ 8,492 FT;</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25343,6 +25421,16 @@
 MD, CON 54 REDUCTORES DE TORQUE INSTALADOS;</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -25396,6 +25484,16 @@
 RETORNOS DE FLUIDO POR TUBERÍA, COMPROBÁNDOSE PRESENCIA DE WASHOUT.</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -25445,6 +25543,16 @@
 SE OBSERVA WASHOUT EN LA JUINTA # 171, PARADA # 57 @ 6,691'.</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -25492,6 +25600,16 @@
           <t>DESCONECTA JUNTA # 171 (SN: 205819), VERIFICA CAUDAL BOMBEADO POR DIRECTA CON;
 LECTURAS DE HERRAMIENTAS DIRECCIONALES: 450 GPM, 1650 PSI, RPM EN EL IMPELER;
 3400, ESPERADO 3500, OK + REMPLAZA JUNTA DP 5 ½”.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -25544,6 +25662,16 @@
 REALIZA PRUEBAS DE HERRAMIENTAS DIRECCIONALES @ 9,097'.</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -25592,6 +25720,16 @@
 M/ LWD (BHA #03) CON PARAMETROS NORMALES EN FORMACION TENA, DESDE 9,111';
 HASTA 9,143' MD — ROP PROM: 32 ft/hr. -- MW: 9.6 PPG;
 Incident Comments:</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -26296,6 +26434,16 @@
 DE 9.6 PPG X 120 SQT @ 9,431' -- REALIZA 2 REPASOS C/ PARADA PERFORADA;</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -26349,6 +26497,16 @@
 FT + 40 BBL DE PILDORA VISCOSA DE 9.6 PPG X 120 SQT @ 9,521 FT;</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -26401,6 +26559,16 @@
 TUBERIA;</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -26451,6 +26619,16 @@
 ELEVADORES -- PRUEBA CON 50 KLBS DE OVERPULL;</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -26499,6 +26677,16 @@
 5 1/2" TRABAJANDO RESTRICCION @ 7,715' MD CON BOMBA Y ROTACION, APLICANDO UN;
 OVERPULL 50 KLBS;
 Incident Comments:</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -27161,6 +27349,16 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -27209,6 +27407,16 @@
 EN DP DE 5 1/2" DESDE 7,715' HASTA 6,691' MD, OBSERVANDO WASHOUT EN JTA. DE 5 1/2";
 DP #171, DE PARADA #57;
 NPT A CARGO DE SINOPEC;</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -27263,6 +27471,16 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -27315,6 +27533,16 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -27362,6 +27590,16 @@
           <t>CON TCOS. DE HAL SPERRY, REALIZA REUNION DE SEGURIDAD CON EL PERSONAL;
 INVOLUCRADO PARA DESARME DE ENSAMBLAJE DIRECCIONAL DE 8 1/2";
 NPT A CARGO DE SINOPEC;</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -27430,6 +27668,16 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -27479,6 +27727,16 @@
 PARADAS DESARAMADAS: 110, 330 JUNTAS DE DP 5 1/2". -- RETIRA 75 REDUCTORES DE;
 TORQUE DE LA SARTA.
 NPT A CARGO DE SINOPEC;</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -27531,6 +27789,16 @@
 LBS-FT.
 NPT A CARGO DE SINOPEC;
 Incident Comments:</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -30633,6 +30901,16 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -30678,6 +30956,16 @@
       <c r="I124" t="inlineStr">
         <is>
           <t>RIG SERVICE -- ENGRASA BLOCK, DRAWWORKS, WASH PIPE DE TOP DRIVE;</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -30727,6 +31015,16 @@
           <t>HAL SPERRY REALIZA REUINON DE SEGURIDAD PARA ARMADO DE NUEVO BHA DIR. DE 8;
 1/2" (BHA #04);
 NPT A CARGO DE SINOPEC;</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -30804,6 +31102,16 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -30856,6 +31164,16 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -30902,6 +31220,16 @@
         <is>
           <t>TCOS. HAL SPERRY INSTALAN FUENTE RADIOACTIVA EN HERRAMIENTAS LWD TRIPLE;
 COMBO;</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -30954,6 +31282,16 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -31002,6 +31340,16 @@
 M/ LWD (BHA #04) EN PARADAS DE 5 1/2" DP, JSHET-54 DESDE 1,321' MD HASTA 5,000' MD;
 NPT A CARGO DE SINOPEC;
 Incident Comments:</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>SC</t>
         </is>
       </c>
     </row>
@@ -33327,6 +33675,16 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -33378,6 +33736,16 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -33425,6 +33793,16 @@
           <t>CIRCULA HOYO CON 400 GPM, 1650 PSI + BOMBEA 40 BBL DE PILDORA DE BAJA;
 REOLOGIA;
 **REALIZA RIG SERVICE = ENGRASA BLOCK, DRAWWORKS, WASH PIPE DE TOP DRIVE;</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -33478,6 +33856,16 @@
 PESOS DE SARTA: P/U WT: 390 KLBS, S/O WT: 200 KLBS, ROT WT: 175 KLBS;</t>
         </is>
       </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -33527,6 +33915,16 @@
 CON 430 GPM,;</t>
         </is>
       </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -33575,6 +33973,16 @@
 DE 10.6 ppg;</t>
         </is>
       </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -33622,6 +34030,16 @@
           <t>LIMPIA CANALETAS Y BOLSILLO + CAMBIA MALLAS DE ZARANDAS;</t>
         </is>
       </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -33667,6 +34085,16 @@
       <c r="I182" t="inlineStr">
         <is>
           <t>ENVIA COMANDOS PARA ICRUISE + TOMA PRESIONES REDUCIDAS DE BOMBA @ 9,874' MD;</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -33719,6 +34147,16 @@
 PARAMETROS: 430 GPM, 120 RPM, WOB: 30-32 KLBS, TQ: 18-22 KLBS-FT;</t>
         </is>
       </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -33767,6 +34205,16 @@
 1/2", ICRUISE Y HTAS. M/ LWD (BHA #04) CONTROLANDO PARAMETROS, PREVIO INGRESO;
 A BASAL TENA, DESDE 9,937' HASTA 10032' MD -- ROP PROM: 47.5 PPH, MW: 10.6 LPG.
 PARAMETROS: 400 GPM, 1800 PSI, 60 RPM, WOB: 10-15 KLBS, TQ: 15-21 KLBS-PIE.</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -33828,6 +34276,16 @@
 10% CALIZA;
 TOTAL REDUCTORES DE TORQUE 5 1/2" DE WWT INSTALADOS = 90;
 Incident Comments:</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -37957,7 +38415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -37969,6 +38427,8 @@
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38015,6 +38475,16 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>operation_details</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>system_op_type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>confirmed_op_type</t>
         </is>
       </c>
     </row>

--- a/outputs/report_database.xlsx
+++ b/outputs/report_database.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -651,7 +650,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -714,7 +712,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -777,7 +774,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -974,7 +970,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1104,7 +1099,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1167,7 +1161,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1230,7 +1223,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1293,7 +1285,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1423,7 +1414,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1486,7 +1476,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1549,7 +1538,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1679,7 +1667,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1809,7 +1796,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1872,7 +1858,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1935,7 +1920,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2132,7 +2116,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2195,7 +2178,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2258,7 +2240,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2321,7 +2302,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2384,7 +2364,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2447,7 +2426,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2510,7 +2488,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2573,7 +2550,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2636,7 +2612,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2699,7 +2674,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2762,7 +2736,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2825,7 +2798,6 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2891,6 +2863,73 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>perforation_intervals row 1 date is in the future</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>drilling:TCHA-006I:2026-06-10:5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>drilling</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>06102026-TCHA-006I-SIN-168-PEC-005-V1R1-REPORTE DIARIO DE MOVILIZACIÓN.pdf</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>pdf_report_parser_v1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>TCHA-006I</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>00 SINOPEC 168</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:28:49+00:00</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:28:49+00:00</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>parsed</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>todayMd missing; progress missing; mudType missing; mudDensity missing</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5856,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ22"/>
+  <dimension ref="A1:BJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -11498,6 +11537,154 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>drilling:TCHA-006I:2026-06-10:5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MAJOR RIG MOVE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TCHA-006I</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>00 SINOPEC 168</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>INICIAL MOVE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>XXXXXXX</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ORIGINAL KB @851.00ft</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ESPERANDO LUZ DEL DÍA PARA CONTINUAR CON LA MOVILIZACIÓN DEL RIG SINOPEC-168.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>RDS + MOVILIZA, RECIBE Y UBICA 19 CARGAS DESDE BASE COCA HASTA LA PLATAFORMA TUICH A. RIG MOVE: 69%. RIG UP: 28%.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>CONTINUAR MOVILIZACIÓN DEL RIG SINOPEC-168 HACIA LA PLATAFORMA TUICH A, POZO TCHA-006I.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>** CUADRILLA COMPLETA SEGÚN CONTRATO Nro. 2025506. ** EQUIPO DE LA CONTRATISTA COMPLETO. ** EQUIPO PESADO CÍA. NOROCCIDENTAL EN SANTA ELENA. 1 GRÚA 90 TON, PLACA 18.25-22002339, INGRESA EL 06/06/2026 A LAS 06H00, GUÍA # 0177005 1 WINCHE, PLACA KAA -1806, INGRESA EL 06/06/2026 A LAS 06H00, GUÍA # 0177006 1 GRÚA 100 TON, PLACA 18.25-22002519, INGRESA EL 05/06/2026 A LAS 06H00, GUÍA # 0177003 1 GRÚA 80 TON, PLACA 18.11-13-002578, INGRESA EL 09/06/2026 A LAS 06H00, GUÍA # 0177011. ** EQUIPO PESADO CÍA. NOROCCIDENTAL EN BASE COCA. 1 GRÚA DE 90 TON, PLACA 18.10-22-002133, INGRESA EL 05/06/2026 A LAS 06H00, GUÍA # 0177008 1 MONTACARGAS DE 12 TON, PLACA 4.1-22-002246, INGRESA EL 05/06/2026 A LAS 06H00, GUÍA # 0177002 1 GRÚA 100 TON, PLACA 18.25-22-002437, INGRESA EL 07/06/2026 A LAS 06H00, GUÍA # 0177009 ENVÍA 19 CARGAS: -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA KAA -1359, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177075). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA PAE -4171, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177088). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA PAE -4365, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177083). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -0636, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177073). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -1178, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177084). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -1360, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177089). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -1421, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177080). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -1435, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177092). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -1569, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177081). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -2084, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177082). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -2416, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177079). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -2945, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177085). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -3135, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177074). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -3206, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177091). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -3435, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177087). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -3442, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177086). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAB -0309, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177076). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA XAI -0376, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177090). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -1772, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177077).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>Environ Incident? N Days since Last LTA : 5.00INCIDENTES SIN REPORTAR EN LAS ULTIMAS 24 HORAS.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24163,7 +24350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I191"/>
+  <dimension ref="A1:I194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -34153,6 +34340,196 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>drilling:TCHA-006I:2026-06-10:5</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Pre job safety meeting</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>REALIZA REUNIÓN DE SEGURIDAD PRE OPERACIONAL CON PERSONAL DE SINOPEC Y;
+TNO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>drilling:TCHA-006I:2026-06-10:5</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>MOVE</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>PERSONAL DE SINOPEC-168 PREPARA Y ENVÍA CARGAS DESDE BASE SINOPEC COCA:
+- SCR (GUÍA # 0177075);
+- MISCELÁNEOS (GUÍA # 0177088);
+- SANCOCHO DE TUBERÍA (GUÍA # 0177083);
+- POORBOY (GUÍA # 0177073);
+- CANASTA CON MISCELÁNEOS (GUÍA # 0177084);
+- GENERADOR (GUÍA # 0177089);
+- CASETA DEL SOLDADOR (GUÍA # 0177080);
+- GENERADOR (GUÍA # 0177092);
+- BODEGA HSE + BODEGA DE CABLES (GUÍA # 0177081);
+- TANQUE AZUL (GUÍA # 0177082);
+- MISCELÁNEOS (GUÍA # 0177079);
+- CANASTA TUBERÍA (GUÍA # 0177085);
+- BOMBA DE RÍO + MECHERO (GUÍA # 0177074);
+- GENERADOR (GUÍA # 0177091);
+- CARRETO CABLES + CHOCK MANIFOLD + CASETA PERFORADOR (GUÍA # 0177087);
+- CANASTA CON MISCELÁNEOS (GUÍA # 0177086);
+- TANQUE ROJO + TANQUE BLANCO (GUÍA # 0177076);
+- GENERADOR (GUÍA # 0177090);
+- 2 CASETAS ELÉCTRICAS (GUÍA # 0177077);
+OPERACIONES EN SANTA ELENA (TUICH A):
+- CONTINÚA ARMANDO LÍNEA DE AGUA DEL MINI CAMP.
+- INSTALA SISTEMA ELÉCTRICO DEL MINI CAMP + PRUEBA FUNCIONAMIENTO DEL MINI;
+CAMP.
+- UBICA TANQUE DE LODO #1 + UBICA ZARANDA + TECHO DE TANQUE + DESIFICADOR DE;
+GAS + MUD CLEANER.
+- MIDE MAS TRAZA MEDIDA DE ÁREA DE GENERADOR + UBICA GEOMEMBRANA + MATTING;
+BOARD + SCR #1 + UBICA GENERADOR #1 - 2 -3 – 4.
+- CONFORMANDO CUBETO DE TANQUE DE LODOS (AVANCE 20%);
+- UBICA CANASTA DE ACEITE.
+** CARGAS ENVIADAS HOY: 19;
+** CARGAS TOTALES ENVIADAS: 99/144;
+** RIG MOVE: 69%;
+** RIG UP: 28%;
+** EQUIPO PESADO:
+- SANTA ELENA (TUICH A):
+1 GRÚA 100 TON;
+1 GRÚA 90 TON;
+1 GRÚA 80 TON;
+1 WINCHE;
+1 MONTACARGA (CORRESPONDE AL RIG 168);
+- CAMPAMENTO BASE COCA:
+1 GRÚA 100 TON;
+1 GRÚA 90 TON;
+1 MONTACARGA;</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>drilling:TCHA-006I:2026-06-10:5</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Waiting for night</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>ESPERANDO LUZ DEL DÍA PARA CONTINUAR MOVILIZACIÓN DEL RIG SINOPEC 168 HACIA;
+LA PLATAFORMA TUICH A Y PALMERAS NORTE, POZO TCHA-006I.
+- 19H00 A 20H00 REALIZA COORDINACIÓN DE ACTIVIDADES DE MOVILIZACIÓN CON;
+PERSONAL DE CÍA. SINOPEC Y EP PETROECUADOR.
+Incident Comments: 5.00;</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34164,7 +34541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -34763,6 +35140,33 @@
         </is>
       </c>
       <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>drilling:TCHA-006I:2026-06-10:5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>No daily cost item recorded</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/outputs/report_database.xlsx
+++ b/outputs/report_database.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="records" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="drilling_fields" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="drilling_survey" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="drilling_bha" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="drilling_operations" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="drilling_costs" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="drilling_bulks" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="completion_fields" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="completion_operations" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="completion_bulks" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="completion_costs" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="completion_mud_products" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="completion_intervals" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="workover_fields" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="workover_operations" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="workover_bulks" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="workover_costs" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="workover_mud_products" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="workover_intervals" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="move_fields" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="move_operations" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="records" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="drilling_fields" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="drilling_survey" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="drilling_bha" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="drilling_operations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="drilling_costs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="drilling_bulks" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="completion_fields" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="completion_operations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="completion_bulks" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="completion_costs" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="completion_mud_products" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="completion_intervals" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workover_fields" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workover_operations" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workover_bulks" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workover_costs" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workover_mud_products" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workover_intervals" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="move_fields" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="move_operations" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -808,52 +808,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-22:10</t>
+          <t>completion:GCLH-022:2026-05-27:2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>05-22-2026_DAILY DRILLING REPORT #10_PCNC-039_SNP-248.pdf</t>
+          <t>GCLH-022_完井日报_20260527_Report-02.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>GCLH-022</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 183</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-06-18T14:58:48+00:00</t>
+          <t>2026-06-18T17:22:26+00:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-04T13:21:31+00:00</t>
+          <t>2026-06-22T07:05:57+00:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -868,65 +868,59 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>mudType missing; mudDensity missing</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+          <t>operation hours total 19.00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-13:1</t>
+          <t>completion:GCLH-022:2026-06-06:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>05-13-2026_Daily Drilling Report-001_PCNC-039_SNP-248.pdf</t>
+          <t>GCLH-022_完井日报_20260606_Report-12.pdf</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>GCLH-022</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 183</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-06-18T15:09:29+00:00</t>
+          <t>2026-06-18T17:22:27+00:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:00+00:00</t>
+          <t>2026-06-22T07:05:57+00:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -936,64 +930,59 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>operation hours total 17.00</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-23:11</t>
+          <t>completion:GCLH-022:2026-06-03:9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>05-23-2026_DAILY DRILLING REPORT #11_PCNC-039_SNP-248.pdf</t>
+          <t>GCLH-022_完井日报_20260603_Report-09.pdf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>GCLH-022</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 183</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-06-18T14:58:48+00:00</t>
+          <t>2026-06-18T17:22:27+00:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-04T13:21:31+00:00</t>
+          <t>2026-06-22T07:05:58+00:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1006,62 +995,56 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-18:6</t>
+          <t>completion:GCLH-022:2026-06-01:7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>05-18-2026_DAILY DRILLING REPORT #05_PCNC-039_SNP-248.pdf</t>
+          <t>GCLH-022_完井日报_20260601_Report-07.pdf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>GCLH-022</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 183</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-06-18T14:58:47+00:00</t>
+          <t>2026-06-18T17:22:26+00:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:01+00:00</t>
+          <t>2026-06-22T07:05:58+00:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1071,64 +1054,59 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>mudType missing; mudDensity missing</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-24:12</t>
+          <t>completion:GCLH-022:2026-06-05:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>05-24-2026_DAILY DRILLING REPORT #12_PCNC-039_SNP-248.pdf</t>
+          <t>GCLH-022_完井日报_20260605_Report-11.pdf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>GCLH-022</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 183</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-18T14:58:48+00:00</t>
+          <t>2026-06-18T17:22:27+00:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-04T13:21:31+00:00</t>
+          <t>2026-06-22T07:05:58+00:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1141,62 +1119,56 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-29:17</t>
+          <t>completion:GCLH-022:2026-05-30:5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>05-29-2026_DAILY DRILLING REPORT #17_PCNC-039_SNP-248.pdf</t>
+          <t>GCLH-022_完井日报_20260530_Report-05.pdf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>GCLH-022</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 183</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-18T15:09:28+00:00</t>
+          <t>2026-06-18T17:22:26+00:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:02+00:00</t>
+          <t>2026-06-22T07:05:59+00:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1213,52 +1185,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-15:3</t>
+          <t>completion:GCLH-022:2026-05-29:4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>05-15-2026_DAILY DRILLING REPORT #03_PCNC-039_SNP-248.pdf</t>
+          <t>GCLH-022_完井日报_20260529_Report-04.pdf</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>GCLH-022</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 183</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-06-18T15:09:29+00:00</t>
+          <t>2026-06-18T17:22:26+00:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:02+00:00</t>
+          <t>2026-06-22T07:05:59+00:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1275,52 +1247,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-20:8</t>
+          <t>completion:GCLH-022:2026-05-28:3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>05-20-2026_DAILY DRILLING REPORT #08_PCNC-039_SNP-248.pdf</t>
+          <t>GCLH-022_完井日报_20260528_Report-03.pdf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>GCLH-022</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 183</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-06-18T14:58:47+00:00</t>
+          <t>2026-06-18T17:22:26+00:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:02+00:00</t>
+          <t>2026-06-22T07:05:59+00:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1337,22 +1309,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-31:19</t>
+          <t>completion:GCLH-022:2026-05-31:6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>05-31-2026_DAILY DRILLING REPORT #19_PCNC-039_SNP-248.pdf</t>
+          <t>GCLH-022_完井日报_20260531_Report-06.pdf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1362,27 +1334,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>GCLH-022</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 183</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-06-18T15:09:29+00:00</t>
+          <t>2026-06-18T17:22:26+00:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:03+00:00</t>
+          <t>2026-06-22T07:06:00+00:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1392,64 +1364,59 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>mudType missing; mudDensity missing; operation hours total 8.00</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-27:15</t>
+          <t>completion:GCLH-022:2026-06-04:10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>05-27-2026_DAILY DRILLING REPORT #15_PCNC-039_SNP-248.pdf</t>
+          <t>GCLH-022_完井日报_20260604_Report-10.pdf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>GCLH-022</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 183</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-06-18T14:58:49+00:00</t>
+          <t>2026-06-18T17:22:27+00:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:03+00:00</t>
+          <t>2026-06-22T07:06:00+00:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1466,52 +1433,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-16:4</t>
+          <t>completion:GCLH-022:2026-05-26:1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>05-16-2026_DAILY DRILLING REPORT #04_PCNC-039_SNP-248.pdf</t>
+          <t>GCLH-022_完井日报_20260526_Report-01.pdf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>GCLH-022</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 183</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-06-18T14:58:46+00:00</t>
+          <t>2026-06-18T17:22:25+00:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:03+00:00</t>
+          <t>2026-06-22T07:06:00+00:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1528,52 +1495,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-19:7</t>
+          <t>completion:GCLH-022:2026-06-02:8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>05-19-2026_DAILY DRILLING REPORT #07_PCNC-039_SNP-248.pdf</t>
+          <t>GCLH-022_完井日报_20260602_Report-08.pdf</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>GCLH-022</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 183</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-06-18T14:58:47+00:00</t>
+          <t>2026-06-18T17:22:27+00:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:04+00:00</t>
+          <t>2026-06-22T07:06:00+00:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1590,52 +1557,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-25:13</t>
+          <t>completion:SCHAS-513:2026-06-11:7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>05-25-2026_DAILY DRILLING REPORT #13_PCNC-039_SNP-248.pdf</t>
+          <t>06112026-SCHAS-513-SIN-219-PEC-007-V1R1 REPORTE DIARIO DE COMPLETACIÓN.pdf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>SCHAS-513</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 219</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-18T14:58:48+00:00</t>
+          <t>2026-06-22T07:06:01+00:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-04T13:21:31+00:00</t>
+          <t>2026-06-22T07:06:01+00:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1645,70 +1612,59 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>mudType missing; mudDensity missing</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-28:16</t>
+          <t>completion:LOBC-010:2026-06-11:8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>drilling</t>
+          <t>completion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>05-28-2026_DAILY DRILLING REPORT #16_PCNC-039_SNP-248.pdf</t>
+          <t>06112026-LOBC-010-SIN-127-PEC-008-V1R1-REPORTE DIARIO DE COMPLETACIÓN.pdf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>pdf_report_parser_v1</t>
+          <t>completion_pdf_parser_v1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PCNC-039</t>
+          <t>LOBC-010</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00 SINOPEC 248</t>
+          <t>SINOPEC 127</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-06-18T15:09:28+00:00</t>
+          <t>2026-06-22T07:06:01+00:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:05+00:00</t>
+          <t>2026-06-22T07:06:01+00:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1718,14 +1674,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>perforation_intervals row 1 date is in the future</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-30:18</t>
+          <t>drilling:PCNC-039:2026-05-22:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1735,7 +1696,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>05-30-2026_DAILY DRILLING REPORT #18_PCNC-039_SNP-248.pdf</t>
+          <t>05-22-2026_DAILY DRILLING REPORT #10_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1745,12 +1706,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1765,12 +1726,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-06-18T15:09:28+00:00</t>
+          <t>2026-06-18T14:58:48+00:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:05+00:00</t>
+          <t>2026-07-05T05:50:51+00:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1792,7 +1753,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-21:9</t>
+          <t>drilling:PCNC-039:2026-05-13:1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1802,7 +1763,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>05-21-2026_DAILY DRILLING REPORT #09_PCNC-039_SNP-248.pdf</t>
+          <t>05-13-2026_Daily Drilling Report-001_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1812,12 +1773,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1832,12 +1793,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-06-18T14:58:47+00:00</t>
+          <t>2026-06-18T15:09:29+00:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:05+00:00</t>
+          <t>2026-07-05T05:50:52+00:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1847,14 +1808,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>operation hours total 17.00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-14:2</t>
+          <t>drilling:PCNC-039:2026-05-23:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1864,7 +1830,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>05-14-2026_DAILY DRILLING REPORT #02_PCNC-039_SNP-248.pdf</t>
+          <t>05-23-2026_DAILY DRILLING REPORT #11_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1874,12 +1840,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1894,12 +1860,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-06-18T14:23:19+00:00</t>
+          <t>2026-06-18T14:58:48+00:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:06+00:00</t>
+          <t>2026-07-05T05:50:52+00:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1916,7 +1882,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-26:14</t>
+          <t>drilling:PCNC-039:2026-05-18:6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1926,7 +1892,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>05-26-2026_DAILY DRILLING REPORT #14_PCNC-039_SNP-248.pdf</t>
+          <t>05-18-2026_DAILY DRILLING REPORT #05_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1936,12 +1902,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1956,12 +1922,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-06-18T14:58:48+00:00</t>
+          <t>2026-06-18T14:58:47+00:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-04T13:21:31+00:00</t>
+          <t>2026-07-05T05:50:52+00:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1971,20 +1937,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>mudType missing; mudDensity missing</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>drilling:PCNC-039:2026-05-17:5</t>
+          <t>drilling:PCNC-039:2026-05-24:12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1994,7 +1959,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>05-17-2026_DAILY DRILLING REPORT #05_PCNC-039_SNP-248.pdf</t>
+          <t>05-24-2026_DAILY DRILLING REPORT #12_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2004,12 +1969,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2024,12 +1989,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-06-18T14:58:46+00:00</t>
+          <t>2026-06-18T14:58:48+00:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-06-22T06:56:06+00:00</t>
+          <t>2026-07-05T05:50:53+00:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2039,64 +2004,59 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>mudType missing; mudDensity missing</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>completion:GCLH-022:2026-05-27:2</t>
+          <t>drilling:PCNC-039:2026-05-29:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GCLH-022_完井日报_20260527_Report-02.pdf</t>
+          <t>05-29-2026_DAILY DRILLING REPORT #17_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>GCLH-022</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SINOPEC 183</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-06-18T17:22:26+00:00</t>
+          <t>2026-06-18T15:09:28+00:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-06-22T07:05:57+00:00</t>
+          <t>2026-07-05T05:50:53+00:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2106,64 +2066,59 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>operation hours total 19.00</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>completion:GCLH-022:2026-06-06:12</t>
+          <t>drilling:PCNC-039:2026-05-15:3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GCLH-022_完井日报_20260606_Report-12.pdf</t>
+          <t>05-15-2026_DAILY DRILLING REPORT #03_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GCLH-022</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SINOPEC 183</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-06-18T17:22:27+00:00</t>
+          <t>2026-06-18T15:09:29+00:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-06-22T07:05:57+00:00</t>
+          <t>2026-07-05T05:50:54+00:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2180,52 +2135,52 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>completion:GCLH-022:2026-06-03:9</t>
+          <t>drilling:PCNC-039:2026-05-20:8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GCLH-022_完井日报_20260603_Report-09.pdf</t>
+          <t>05-20-2026_DAILY DRILLING REPORT #08_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>GCLH-022</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SINOPEC 183</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-06-18T17:22:27+00:00</t>
+          <t>2026-06-18T14:58:47+00:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-06-22T07:05:58+00:00</t>
+          <t>2026-07-05T05:50:54+00:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2242,52 +2197,52 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>completion:GCLH-022:2026-06-01:7</t>
+          <t>drilling:PCNC-039:2026-05-31:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GCLH-022_完井日报_20260601_Report-07.pdf</t>
+          <t>05-31-2026_DAILY DRILLING REPORT #19_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GCLH-022</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SINOPEC 183</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-06-18T17:22:26+00:00</t>
+          <t>2026-06-18T15:09:29+00:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-06-22T07:05:58+00:00</t>
+          <t>2026-07-05T05:50:54+00:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2297,59 +2252,64 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>mudType missing; mudDensity missing; operation hours total 8.00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>completion:GCLH-022:2026-06-05:11</t>
+          <t>drilling:PCNC-039:2026-05-27:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GCLH-022_完井日报_20260605_Report-11.pdf</t>
+          <t>05-27-2026_DAILY DRILLING REPORT #15_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GCLH-022</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SINOPEC 183</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-06-18T17:22:27+00:00</t>
+          <t>2026-06-18T14:58:49+00:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-06-22T07:05:58+00:00</t>
+          <t>2026-07-05T05:50:55+00:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2366,52 +2326,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>completion:GCLH-022:2026-05-30:5</t>
+          <t>drilling:PCNC-039:2026-05-16:4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GCLH-022_完井日报_20260530_Report-05.pdf</t>
+          <t>05-16-2026_DAILY DRILLING REPORT #04_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>GCLH-022</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SINOPEC 183</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-06-18T17:22:26+00:00</t>
+          <t>2026-06-18T14:58:46+00:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-06-22T07:05:59+00:00</t>
+          <t>2026-07-05T05:50:55+00:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2428,52 +2388,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>completion:GCLH-022:2026-05-29:4</t>
+          <t>drilling:PCNC-039:2026-05-19:7</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GCLH-022_完井日报_20260529_Report-04.pdf</t>
+          <t>05-19-2026_DAILY DRILLING REPORT #07_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GCLH-022</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SINOPEC 183</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-06-18T17:22:26+00:00</t>
+          <t>2026-06-18T14:58:47+00:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-06-22T07:05:59+00:00</t>
+          <t>2026-07-05T05:50:56+00:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2490,52 +2450,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>completion:GCLH-022:2026-05-28:3</t>
+          <t>drilling:PCNC-039:2026-05-25:13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GCLH-022_完井日报_20260528_Report-03.pdf</t>
+          <t>05-25-2026_DAILY DRILLING REPORT #13_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>GCLH-022</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SINOPEC 183</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-06-18T17:22:26+00:00</t>
+          <t>2026-06-18T14:58:48+00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-06-22T07:05:59+00:00</t>
+          <t>2026-07-05T05:50:56+00:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2545,59 +2505,64 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>mudType missing; mudDensity missing</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>completion:GCLH-022:2026-05-31:6</t>
+          <t>drilling:PCNC-039:2026-05-28:16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GCLH-022_完井日报_20260531_Report-06.pdf</t>
+          <t>05-28-2026_DAILY DRILLING REPORT #16_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>GCLH-022</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SINOPEC 183</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-06-18T17:22:26+00:00</t>
+          <t>2026-06-18T15:09:28+00:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-06-22T07:06:00+00:00</t>
+          <t>2026-07-05T05:50:56+00:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2614,52 +2579,52 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>completion:GCLH-022:2026-06-04:10</t>
+          <t>drilling:PCNC-039:2026-05-30:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GCLH-022_完井日报_20260604_Report-10.pdf</t>
+          <t>05-30-2026_DAILY DRILLING REPORT #18_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>GCLH-022</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SINOPEC 183</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-06-18T17:22:27+00:00</t>
+          <t>2026-06-18T15:09:28+00:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-06-22T07:06:00+00:00</t>
+          <t>2026-07-05T05:50:57+00:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2669,59 +2634,64 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>mudType missing; mudDensity missing</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>completion:GCLH-022:2026-05-26:1</t>
+          <t>drilling:PCNC-039:2026-05-21:9</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GCLH-022_完井日报_20260526_Report-01.pdf</t>
+          <t>05-21-2026_DAILY DRILLING REPORT #09_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>GCLH-022</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SINOPEC 183</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-06-18T17:22:25+00:00</t>
+          <t>2026-06-18T14:58:47+00:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-06-22T07:06:00+00:00</t>
+          <t>2026-07-05T05:50:57+00:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2738,52 +2708,52 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>completion:GCLH-022:2026-06-02:8</t>
+          <t>drilling:PCNC-039:2026-05-14:2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GCLH-022_完井日报_20260602_Report-08.pdf</t>
+          <t>05-14-2026_DAILY DRILLING REPORT #02_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>GCLH-022</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SINOPEC 183</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-06-18T17:22:27+00:00</t>
+          <t>2026-06-18T14:23:19+00:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-06-22T07:06:00+00:00</t>
+          <t>2026-07-05T05:50:57+00:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2800,52 +2770,52 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>completion:SCHAS-513:2026-06-11:7</t>
+          <t>drilling:PCNC-039:2026-05-26:14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>06112026-SCHAS-513-SIN-219-PEC-007-V1R1 REPORTE DIARIO DE COMPLETACIÓN.pdf</t>
+          <t>05-26-2026_DAILY DRILLING REPORT #14_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SCHAS-513</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SINOPEC 219</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-06-22T07:06:01+00:00</t>
+          <t>2026-06-18T14:58:48+00:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-06-22T07:06:01+00:00</t>
+          <t>2026-07-05T05:50:58+00:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2862,52 +2832,52 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>completion:LOBC-010:2026-06-11:8</t>
+          <t>drilling:PCNC-039:2026-05-17:5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>completion</t>
+          <t>drilling</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>06112026-LOBC-010-SIN-127-PEC-008-V1R1-REPORTE DIARIO DE COMPLETACIÓN.pdf</t>
+          <t>05-17-2026_DAILY DRILLING REPORT #05_PCNC-039_SNP-248.pdf</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>completion_pdf_parser_v1</t>
+          <t>pdf_report_parser_v1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>LOBC-010</t>
+          <t>PCNC-039</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SINOPEC 127</t>
+          <t>00 SINOPEC 248</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-06-22T07:06:01+00:00</t>
+          <t>2026-06-18T14:58:46+00:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-06-22T07:06:01+00:00</t>
+          <t>2026-07-05T05:50:58+00:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2922,9 +2892,81 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>perforation_intervals row 1 date is in the future</t>
-        </is>
-      </c>
+          <t>mudType missing; mudDensity missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>drilling:TCHA-006I:2026-06-10:5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>drilling</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>06102026-TCHA-006I-SIN-168-PEC-005-V1R1-REPORTE DIARIO DE MOVILIZACIÓN.pdf</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>pdf_report_parser_v1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>TCHA-006I</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>00 SINOPEC 168</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-07-05T05:51:20+00:00</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-07-05T05:51:20+00:00</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>parsed</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>todayMd missing; progress missing; mudType missing; mudDensity missing</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5861,11 +5903,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ22"/>
+  <dimension ref="A1:BJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -11542,6 +11584,154 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>drilling:TCHA-006I:2026-06-10:5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MAJOR RIG MOVE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TCHA-006I</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>00 SINOPEC 168</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>INICIAL MOVE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>XXXXXXX</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ORIGINAL KB @851.00ft</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ESPERANDO LUZ DEL DÍA PARA CONTINUAR CON LA MOVILIZACIÓN DEL RIG SINOPEC-168.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>RDS + MOVILIZA, RECIBE Y UBICA 19 CARGAS DESDE BASE COCA HASTA LA PLATAFORMA TUICH A. RIG MOVE: 69%. RIG UP: 28%.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>CONTINUAR MOVILIZACIÓN DEL RIG SINOPEC-168 HACIA LA PLATAFORMA TUICH A, POZO TCHA-006I.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>** CUADRILLA COMPLETA SEGÚN CONTRATO Nro. 2025506. ** EQUIPO DE LA CONTRATISTA COMPLETO. ** EQUIPO PESADO CÍA. NOROCCIDENTAL EN SANTA ELENA. 1 GRÚA 90 TON, PLACA 18.25-22002339, INGRESA EL 06/06/2026 A LAS 06H00, GUÍA # 0177005 1 WINCHE, PLACA KAA -1806, INGRESA EL 06/06/2026 A LAS 06H00, GUÍA # 0177006 1 GRÚA 100 TON, PLACA 18.25-22002519, INGRESA EL 05/06/2026 A LAS 06H00, GUÍA # 0177003 1 GRÚA 80 TON, PLACA 18.11-13-002578, INGRESA EL 09/06/2026 A LAS 06H00, GUÍA # 0177011. ** EQUIPO PESADO CÍA. NOROCCIDENTAL EN BASE COCA. 1 GRÚA DE 90 TON, PLACA 18.10-22-002133, INGRESA EL 05/06/2026 A LAS 06H00, GUÍA # 0177008 1 MONTACARGAS DE 12 TON, PLACA 4.1-22-002246, INGRESA EL 05/06/2026 A LAS 06H00, GUÍA # 0177002 1 GRÚA 100 TON, PLACA 18.25-22-002437, INGRESA EL 07/06/2026 A LAS 06H00, GUÍA # 0177009 ENVÍA 19 CARGAS: -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA KAA -1359, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177075). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA PAE -4171, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177088). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA PAE -4365, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177083). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -0636, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177073). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -1178, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177084). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -1360, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177089). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -1421, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177080). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -1435, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177092). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -1569, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177081). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -2084, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177082). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -2416, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177079). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -2945, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177085). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -3135, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177074). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -3206, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177091). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -3435, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177087). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -3442, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177086). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAB -0309, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177076). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA XAI -0376, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177090). -CABEZAL ADAPTABLE CON CAMA BAJA Y CAMA ALTA, PLACA QAA -1772, INGRESA EL 09/06/2026, REALIZA UN VIAJE SEGÚN (GUÍA # 0177077).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>Environ Incident? N Days since Last LTA : 5.00INCIDENTES SIN REPORTAR EN LAS ULTIMAS 24 HORAS.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24219,7 +24409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K191"/>
+  <dimension ref="A1:K194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -25351,16 +25541,6 @@
 PILDORA SELLANTE DE 9.6 PPG X 40 SQT @ 8,492 FT;</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25421,16 +25601,6 @@
 MD, CON 54 REDUCTORES DE TORQUE INSTALADOS;</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -25484,16 +25654,6 @@
 RETORNOS DE FLUIDO POR TUBERÍA, COMPROBÁNDOSE PRESENCIA DE WASHOUT.</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -25543,16 +25703,6 @@
 SE OBSERVA WASHOUT EN LA JUINTA # 171, PARADA # 57 @ 6,691'.</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -25600,16 +25750,6 @@
           <t>DESCONECTA JUNTA # 171 (SN: 205819), VERIFICA CAUDAL BOMBEADO POR DIRECTA CON;
 LECTURAS DE HERRAMIENTAS DIRECCIONALES: 450 GPM, 1650 PSI, RPM EN EL IMPELER;
 3400, ESPERADO 3500, OK + REMPLAZA JUNTA DP 5 ½”.</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -25662,16 +25802,6 @@
 REALIZA PRUEBAS DE HERRAMIENTAS DIRECCIONALES @ 9,097'.</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -25720,16 +25850,6 @@
 M/ LWD (BHA #03) CON PARAMETROS NORMALES EN FORMACION TENA, DESDE 9,111';
 HASTA 9,143' MD — ROP PROM: 32 ft/hr. -- MW: 9.6 PPG;
 Incident Comments:</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -26434,16 +26554,6 @@
 DE 9.6 PPG X 120 SQT @ 9,431' -- REALIZA 2 REPASOS C/ PARADA PERFORADA;</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -26497,16 +26607,6 @@
 FT + 40 BBL DE PILDORA VISCOSA DE 9.6 PPG X 120 SQT @ 9,521 FT;</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -26559,16 +26659,6 @@
 TUBERIA;</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -26619,16 +26709,6 @@
 ELEVADORES -- PRUEBA CON 50 KLBS DE OVERPULL;</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -26677,16 +26757,6 @@
 5 1/2" TRABAJANDO RESTRICCION @ 7,715' MD CON BOMBA Y ROTACION, APLICANDO UN;
 OVERPULL 50 KLBS;
 Incident Comments:</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -27349,16 +27419,6 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -27407,16 +27467,6 @@
 EN DP DE 5 1/2" DESDE 7,715' HASTA 6,691' MD, OBSERVANDO WASHOUT EN JTA. DE 5 1/2";
 DP #171, DE PARADA #57;
 NPT A CARGO DE SINOPEC;</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -27471,16 +27521,6 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -27533,16 +27573,6 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -27590,16 +27620,6 @@
           <t>CON TCOS. DE HAL SPERRY, REALIZA REUNION DE SEGURIDAD CON EL PERSONAL;
 INVOLUCRADO PARA DESARME DE ENSAMBLAJE DIRECCIONAL DE 8 1/2";
 NPT A CARGO DE SINOPEC;</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -27668,16 +27688,6 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -27727,16 +27737,6 @@
 PARADAS DESARAMADAS: 110, 330 JUNTAS DE DP 5 1/2". -- RETIRA 75 REDUCTORES DE;
 TORQUE DE LA SARTA.
 NPT A CARGO DE SINOPEC;</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -27789,16 +27789,6 @@
 LBS-FT.
 NPT A CARGO DE SINOPEC;
 Incident Comments:</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -30901,16 +30891,6 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -30956,16 +30936,6 @@
       <c r="I124" t="inlineStr">
         <is>
           <t>RIG SERVICE -- ENGRASA BLOCK, DRAWWORKS, WASH PIPE DE TOP DRIVE;</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -31015,16 +30985,6 @@
           <t>HAL SPERRY REALIZA REUINON DE SEGURIDAD PARA ARMADO DE NUEVO BHA DIR. DE 8;
 1/2" (BHA #04);
 NPT A CARGO DE SINOPEC;</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -31102,16 +31062,6 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -31164,16 +31114,6 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -31220,16 +31160,6 @@
         <is>
           <t>TCOS. HAL SPERRY INSTALAN FUENTE RADIOACTIVA EN HERRAMIENTAS LWD TRIPLE;
 COMBO;</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>NPT</t>
         </is>
       </c>
     </row>
@@ -31282,16 +31212,6 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -31340,16 +31260,6 @@
 M/ LWD (BHA #04) EN PARADAS DE 5 1/2" DP, JSHET-54 DESDE 1,321' MD HASTA 5,000' MD;
 NPT A CARGO DE SINOPEC;
 Incident Comments:</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>SC</t>
         </is>
       </c>
     </row>
@@ -33675,16 +33585,6 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -33736,16 +33636,6 @@
 NPT A CARGO DE SINOPEC;</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>NPT</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -33793,16 +33683,6 @@
           <t>CIRCULA HOYO CON 400 GPM, 1650 PSI + BOMBEA 40 BBL DE PILDORA DE BAJA;
 REOLOGIA;
 **REALIZA RIG SERVICE = ENGRASA BLOCK, DRAWWORKS, WASH PIPE DE TOP DRIVE;</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -33856,16 +33736,6 @@
 PESOS DE SARTA: P/U WT: 390 KLBS, S/O WT: 200 KLBS, ROT WT: 175 KLBS;</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -33915,16 +33785,6 @@
 CON 430 GPM,;</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -33973,16 +33833,6 @@
 DE 10.6 ppg;</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -34030,16 +33880,6 @@
           <t>LIMPIA CANALETAS Y BOLSILLO + CAMBIA MALLAS DE ZARANDAS;</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -34085,16 +33925,6 @@
       <c r="I182" t="inlineStr">
         <is>
           <t>ENVIA COMANDOS PARA ICRUISE + TOMA PRESIONES REDUCIDAS DE BOMBA @ 9,874' MD;</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -34147,16 +33977,6 @@
 PARAMETROS: 430 GPM, 120 RPM, WOB: 30-32 KLBS, TQ: 18-22 KLBS-FT;</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -34205,16 +34025,6 @@
 1/2", ICRUISE Y HTAS. M/ LWD (BHA #04) CONTROLANDO PARAMETROS, PREVIO INGRESO;
 A BASAL TENA, DESDE 9,937' HASTA 10032' MD -- ROP PROM: 47.5 PPH, MW: 10.6 LPG.
 PARAMETROS: 400 GPM, 1800 PSI, 60 RPM, WOB: 10-15 KLBS, TQ: 15-21 KLBS-PIE.</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -34278,16 +34088,6 @@
 Incident Comments:</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -34611,6 +34411,202 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>drilling:TCHA-006I:2026-06-10:5</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Pre job safety meeting</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>REALIZA REUNIÓN DE SEGURIDAD PRE OPERACIONAL CON PERSONAL DE SINOPEC Y;
+TNO.</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>drilling:TCHA-006I:2026-06-10:5</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>MOVE</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>PERSONAL DE SINOPEC-168 PREPARA Y ENVÍA CARGAS DESDE BASE SINOPEC COCA:
+- SCR (GUÍA # 0177075);
+- MISCELÁNEOS (GUÍA # 0177088);
+- SANCOCHO DE TUBERÍA (GUÍA # 0177083);
+- POORBOY (GUÍA # 0177073);
+- CANASTA CON MISCELÁNEOS (GUÍA # 0177084);
+- GENERADOR (GUÍA # 0177089);
+- CASETA DEL SOLDADOR (GUÍA # 0177080);
+- GENERADOR (GUÍA # 0177092);
+- BODEGA HSE + BODEGA DE CABLES (GUÍA # 0177081);
+- TANQUE AZUL (GUÍA # 0177082);
+- MISCELÁNEOS (GUÍA # 0177079);
+- CANASTA TUBERÍA (GUÍA # 0177085);
+- BOMBA DE RÍO + MECHERO (GUÍA # 0177074);
+- GENERADOR (GUÍA # 0177091);
+- CARRETO CABLES + CHOCK MANIFOLD + CASETA PERFORADOR (GUÍA # 0177087);
+- CANASTA CON MISCELÁNEOS (GUÍA # 0177086);
+- TANQUE ROJO + TANQUE BLANCO (GUÍA # 0177076);
+- GENERADOR (GUÍA # 0177090);
+- 2 CASETAS ELÉCTRICAS (GUÍA # 0177077);
+OPERACIONES EN SANTA ELENA (TUICH A):
+- CONTINÚA ARMANDO LÍNEA DE AGUA DEL MINI CAMP.
+- INSTALA SISTEMA ELÉCTRICO DEL MINI CAMP + PRUEBA FUNCIONAMIENTO DEL MINI;
+CAMP.
+- UBICA TANQUE DE LODO #1 + UBICA ZARANDA + TECHO DE TANQUE + DESIFICADOR DE;
+GAS + MUD CLEANER.
+- MIDE MAS TRAZA MEDIDA DE ÁREA DE GENERADOR + UBICA GEOMEMBRANA + MATTING;
+BOARD + SCR #1 + UBICA GENERADOR #1 - 2 -3 – 4.
+- CONFORMANDO CUBETO DE TANQUE DE LODOS (AVANCE 20%);
+- UBICA CANASTA DE ACEITE.
+** CARGAS ENVIADAS HOY: 19;
+** CARGAS TOTALES ENVIADAS: 99/144;
+** RIG MOVE: 69%;
+** RIG UP: 28%;
+** EQUIPO PESADO:
+- SANTA ELENA (TUICH A):
+1 GRÚA 100 TON;
+1 GRÚA 90 TON;
+1 GRÚA 80 TON;
+1 WINCHE;
+1 MONTACARGA (CORRESPONDE AL RIG 168);
+- CAMPAMENTO BASE COCA:
+1 GRÚA 100 TON;
+1 GRÚA 90 TON;
+1 MONTACARGA;</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>drilling:TCHA-006I:2026-06-10:5</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Waiting for night</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>ESPERANDO LUZ DEL DÍA PARA CONTINUAR MOVILIZACIÓN DEL RIG SINOPEC 168 HACIA;
+LA PLATAFORMA TUICH A Y PALMERAS NORTE, POZO TCHA-006I.
+- 19H00 A 20H00 REALIZA COORDINACIÓN DE ACTIVIDADES DE MOVILIZACIÓN CON;
+PERSONAL DE CÍA. SINOPEC Y EP PETROECUADOR.
+Incident Comments: 5.00;</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34622,7 +34618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -35221,6 +35217,33 @@
         </is>
       </c>
       <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>drilling:TCHA-006I:2026-06-10:5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>No daily cost item recorded</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/outputs/report_database.xlsx
+++ b/outputs/report_database.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-07-10T14:47:11+00:00</t>
+          <t>2026-07-10T15:45:00+00:00</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:01+00:00</t>
+          <t>2026-07-10T15:45:03+00:00</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:02+00:00</t>
+          <t>2026-07-10T15:45:05+00:00</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:01+00:00</t>
+          <t>2026-07-10T15:45:03+00:00</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:02+00:00</t>
+          <t>2026-07-10T15:45:04+00:00</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:01+00:00</t>
+          <t>2026-07-10T15:45:03+00:00</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-07-10T14:47:11+00:00</t>
+          <t>2026-07-10T15:45:02+00:00</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:02+00:00</t>
+          <t>2026-07-10T15:45:04+00:00</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:01+00:00</t>
+          <t>2026-07-10T15:45:04+00:00</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>QUEUED</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-07-10T14:55:23+00:00</t>
+          <t>2026-07-10T15:45:01+00:00</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:01+00:00</t>
+          <t>2026-07-10T15:45:02+00:00</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:02+00:00</t>
+          <t>2026-07-10T15:45:04+00:00</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:02+00:00</t>
+          <t>2026-07-10T15:45:04+00:00</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:01+00:00</t>
+          <t>2026-07-10T15:45:03+00:00</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>QUEUED</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-07-10T14:25:12+00:00</t>
+          <t>2026-07-10T15:45:02+00:00</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-07-10T14:47:11+00:00</t>
+          <t>2026-07-10T15:45:01+00:00</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:01+00:00</t>
+          <t>2026-07-10T15:45:03+00:00</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:02+00:00</t>
+          <t>2026-07-10T15:45:05+00:00</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:01+00:00</t>
+          <t>2026-07-10T15:45:02+00:00</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2026-07-10T13:37:02+00:00</t>
+          <t>2026-07-10T15:45:04+00:00</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2341,14 +2341,15 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2026-07-10T15:08:02+00:00</t>
+          <t>2026-07-10T15:46:43+00:00</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2403,12 +2404,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>QUEUED</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>drilling-daily-v3</t>
+          <t>drilling-daily-v4</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2423,15 +2424,14 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026-07-10T15:27:31+00:00</t>
+          <t>2026-07-10T15:45:05+00:00</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3224,7 +3224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P301"/>
+  <dimension ref="A1:P325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -24127,12 +24127,12 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
     </row>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>起出 底部钻具组合 #3 至井口。磨铣 HTAS. 定向和钻头。组装并下入 底部钻具组合 #4 定向，配备 ICRUISE、MWD 及 PDC 钻头 12 1/4" 直至底部 @ 10832'，刷新钻井液 润滑度为 2%。稠化至 10.5 LPG，使用 底部钻具组合 #4（底部钻具组合）进行第 12 又 1/4 英寸井段的钻进</t>
+          <t>起出 底部钻具组合 #3 至井口。磨铣 HTAS. 定向和钻头。组装并下入 底部钻具组合 #4 定向，配备 ICRUISE、MWD 和 PDC 钻头 12 1/4" 直至底部 @ 10832' 刷新钻井液 润滑度为 2%。稠化至 10.5 LPG，使用 底部钻具组合 #4（底部钻具组合）进行第 12 又 1/4 英寸井段的钻进</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -24199,12 +24199,12 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
     </row>
@@ -24271,12 +24271,12 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
     </row>
@@ -24343,12 +24343,12 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
     </row>
@@ -24415,12 +24415,12 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
     </row>
@@ -24487,12 +24487,12 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
     </row>
@@ -24559,12 +24559,12 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
     </row>
@@ -24631,12 +24631,12 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
     </row>
@@ -24703,12 +24703,12 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
     </row>
@@ -24775,12 +24775,12 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
     </row>
@@ -24847,12 +24847,12 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
     </row>
@@ -24919,12 +24919,1740 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>2026-07-10T15:01:57+00:00</t>
+          <t>2026-07-10T15:23:35+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>daily_report</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>report_fields.currentOps</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>SACANDO BHA #3 DIRECCIONAL CON ICRUISE, MWD Y BROCA PDC 12 1/4" EN HOYO ENTUBADO @ 1700 PIES</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>REMOVING BHA #3 DIRECTIONAL WITH ICRUISE, MWD AND 12 1/4" PDC DRILL BIT IN LINED HOLE @ 1700 FEET</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>3d04f5fdeb1cb643192e621d1c1d365e64d1cdc594c3bf777f05a1867c733f55</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>daily_report</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>report_fields.forecast24h</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>SACAR BHA #3 HASTA SUPERFICIE. QUEBRAR HTAS. DIRECCIONALES Y BROCA. ARMAR Y BAJAR BHA #4 DIRECCIONAL CON ICRUISE, MWD Y BROCA PDC 12 1/4" HASTA EL FONDO @ 10832' REFRESCAR FLUIDO Y LUBRICIDAD AL 2%. DENSIFICAR A 10.5 LPG PERFORAR CON BHA #4 SECCION 12 1/4"</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>PULL OUT OF HOLE (POOH) BHA TO SURFACE. BREAK CONNECTIONS AT DIRECTIONAL AND DRILL STRING. RIG UP AND RUN IN HOLE (RIH) WITH BHA #4 DIRECTIONAL EQUIPPED WITH ICRUISE, MWD, AND 12 1/4" PDC DRITLL BIT DOWN TO BOTTOM @ 10832'. REFRESH FLUIDS, ADJUST RHEOLOGY TO 2%. THICKEN UP TO 10.5 LUG PERFORATE WITH BHA #4 SECTION 12 1/4"</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>c2d4196e428a63bbf5b0f12ef93d7409278d508f3ef659f40718a12b2f641438</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>daily_report</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>report_fields.incidentComments</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Environ Incident? N Days since Last LTA 188.00INCIDENTES SIN REPORTAR EN LAS ULTIMAS 24 HORAS.</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>ENVIRON INCIDENT? N DAYS SINCE LAST LTA 188.00 UNREPORTED INCIDENTS IN THE PAST 24 HOURS.</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>320fb51cfe6f7b2054d4d4b5eede085f7ecaf164f93a428ad2438f63eecf7524</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>daily_report</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>report_fields.mudComments</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Durante perforación de formacion Tena bombea píldoras</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>During drilling of formation Tena pumps pills.</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>05683f18e40e86bf9ce56a656b25ad3ceea4130c99d4ebe8ba70ad885ed3ef98</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>daily_report</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>report_fields.otherRemarks</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>POB: MINICAMP 30 PAX CAMPAMENTO 47 PAX -(1) VACUUM (178 BBL): TRASLADO DE FLUIDOS DE AGUA TRATADA DE BSS Y AGUAS GRISES DE CAMPAMENTOS. -(1) VACUUM (130 BBL): TRASLADO DE FLUIDO CONTAMINADOS SNP -248 -PERSONAL APROBADO PARA CAPATAZ DE PERSONAL COMUNITARIO (OBREROS DE PATIO ), ESTE SERVICIO SE BRINDA DESDE EL 22 DE ENERO DE 2026. -SERVICIO DE RIGGER PARA MONTACARGA DESDE EL DIA 27 DE MARZO DEL 2026 -INGRESA DESDE EL 8 DE MAYO 2026 BUSETA PROVISTA POR HALLIBURTON PARA MOVILIZACION DE PERSONAL -INGRESA DESDE EL 8 DE MAYO 2026 CAMA ALTA PROVISTA POR HALLIBURTON PARA MOVILIZAR CARGAS DESDE PUCUNA 6 A PUCUNA C -INGRESA DESDE EL 8 DE MAYO 2026 MONTACARGAS DE 10 TON PROVISTA POR HALLIBURTON PARA CARGAS EN PUCUNA 6 (OPERADOR +RIGGER)+ INGRESA DESDE EL 14 DE MAYO UN OPERADOR DE MONTACARGAS PARA TRABAJO EN LA NOCHE HASTA EL LUNES 18 DE MAYO -PERSONAL DE GLOBAL INSPECCION SE RETIRA DE LOCACION -PERSONAL DE MISSION PETROLEUM INSTALA ANILLOS DE TORQUE 9 5/8IN FECHA DE INGRESO 9 DE JUNIO 2026 -INGRESA PERSONAL DE SINOPEC TUBULARES PARA COORDINAR EL ORDEN DE LA TUBERIA DE LOS RACKS. -INGRESA CEMENTO TIPO A 887 SACOS REPORTE DIARIO *EVACUACIONES DE CORTES DE PERFORACIÓN. TOTAL VOLUMEN DIARIO EVACUADO CORTES NORMALES DE PERFORACIÓN : 80.00 M3 TOTAL VOLUMEN DIARIO EVACUADO CORTES CON CEMENTO = 00.00 M3 N° VIAJES DIARIO = 8 VOLUMEN ACUMULADO CORTES NORMALES = 1855.50 M3 VOLUMEN ACUMULADO CORTES CON CEMENTO = 86.00 M3 TOTAL VIAJES ACUMULADO = 200</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>POB: MINICAMP 30 PAX CAMPAMENTO 47 PAX -(1) VACUUM (178 BBL): TRANSFER OF TREATED WATER FLUIDS FROM BSS AND GREYWATERS FROM CAMPS. -(1) VACUUM (130 BBL): TRANSFER OF CONTAMINATED SNP FLUID -248 -PERSONNEL APPROVED FOR COMMUNITY FOREMAN (COURTYARD WORKERS), THIS SERVICE HAS BEEN PROVIDED SINCE JANUARY 22, JANUARY 2026. -RIGGER SERVICE FOR CRANE LIFTING FROM MARCH 27, 2026 -BUS PROVIDED BY HALLIBURTON FOR PERSONNEL MOBILIZATION ENTERS ON MAY 8, 2026 -ENTERING SINCE MAY 8, 2026 HIGH BED PROVIDED BY HALLIBURTON TO MOBILE LOADS FROM PUCUNA 6 TO PUCUNA C -ENTERING SINCE MAY 8, 2026 CRANE OF 10 TON PROVIDED BY HALLIBURTON FOR LOADS IN PUCUNA 6 (OPERATOR +RIGGER)+ ENTERING SINCE MAY 14 A CRANE OPERATOR TO WORK AT NIGHT UNTIL MONDAY, MAY 18 -PERSONNEL OF GLOBAL INSPECTION WITHDRAW FROM LOCATION -MISSION PETROLEUM PERSONNEL INSTALLS TORQUE RINGS 9 5/8IN DATE OF ENTRY JUNE 9, 2026 - SINOPEC TUBULARS PERSONNEL ENTER TO COORDINATE THE PIPE ORDER FOR THE RACK PIPING. - TYPE A CEMENT 887 BAGS DAILY REPORT *DRILLING CUTtings EVACUATIONS. TOTAL DAILY VOLUME EVACUATED NORMAL DRILLING CUTTINGS: 80.00 M3 TOTAL DAILY VOLUME EVACUATED CEMENTED CUTTINGS = 00.00 M3 NUMBER OF DAILY TRIPS = 8 ACCUMULATED VOLUME CUTtings, NORMAL = 1855.50 M3 ACCUMULATED VOLUME CEMENTED CUTINGS = 86.00 M3 TOTAL ACCUMULATED TRIPS = 200</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>d68721850a25c8aa7aae985a9d565792ac06619d73b047f34a0c312ca7edcc98</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>daily_report</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>report_fields.summary24h</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>PERFORÓ CON BHA #3 DIRECCIONAL CON ICRUISE, MWD Y BROCA PDC 12 1/4" DESDE 10641 PIES HASTA 10832 PIES. BOMBEÓ TREN DE PILDORAS Y CIRCULÓ HASTA RETORNOS LIMPIOS. SACA BHA #3 EN VIAJE A SUPERFICIE PARA CAMBIO DE BHA DESDE 10832 PIES HASTA 1700 PIES</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>DRILLED WITH BHA #3 DIRECTIONAL WITH ICRUISE, MWD AND PDC DRILL BIT 12 1/4" FROM 10641 FEET TO 10832 FEET. PUMPED PILLOW STRING AND CIRCULATED UNTIL CLEAN RETURNS. ROPE BHA #3 ON TRIP TO SURFACE FOR CHANGE OF BHA FROM 10832 FEET TO 1700 FEET</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>01a5b24ac0169764755fa891eb5d68079b9cd31ef1f37f9a9814c19130eb9b38</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11:operations:1</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>operations.operation_details</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>PERFORA CON BHA #3 DIRECCIONAL CON iCRUISE, MWD Y BROCA PDC 12 1/4" ATRAVESANDO; FORMACIÓN TENA DESDE 10641 PIES HASTA 10832 PIES. PARÁMETROS: 1000 GPM, 2800 PSI, 120 RPM, TQ 25–28 KLBS-PIE, WOB 40–50 KLBS. AVANCE: 191 PIES, ROP PROMEDIO: 32 PPH. REALIZA DOS REPASOS CADA PARADA; BOMBEA 60 BBL DE PÍLDORA DE BAJA REOLOGÍA / DISPERSA DE 8.5 LPG x 27 SEG/QT @ 10656'; Y 10755'. ULTIMO SURVEY; 10718' MD / 8442.2' TVD, INC: 43.16°, AZI: 13.07°, CT-CT: 13.1', 10.4' ARRIBA, 8' DERECHA; ULTIMA MUESTRA (TENA) @ 10832'; 100% ARCILLOLITA; BROCA: ROTADOS: 191 PIES, 4.48 HORAS, ROP NETO: 42.63 PPH, 100%; PESO DE SARTA: ARRIBA 430 KLBS, ROTANDO 275 KLBS, ABAJO 190 KLBS. TÉCNICO DE WWT INSTALA REDUCTORES DE TORQUE DESDE PARADA #53 HASTA PARADA #96. TOTAL INSTALADOS: 129/150 UNIDADES.</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>2cf1da753a81ab0834976eca34077332d8f1fb58036d9f2d57264e6fd820248f</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Ollama returned low-quality translation (6::part-3: source text was returned unchanged).</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11:operations:2</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>operations.operation_details</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>HALLIBURTON SPERRY REALIZA RESETEO DE HERRAMIENTAS DIRECCIONALES Y ENVÍA; DOWNLINK PARA iCRUISE,; **NOTA**; DEBIDO A FALLA / COMPORTAMIENTO ANÓMALO DE HERRAMIENTA DIRECCIONAL, SE DECIDE; REALIZAR VIAJE A SUPERFICIE PARA CAMBIO DE BHA #3.</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>HALLIBURTON SPERRY PERFORMS RESET OF DIRECTIONAL TOOLS AND SENDS; DOWNLINK FOR iCRUISE, **NOTE**; DUE TO FAILURE / ABNORMAL BEHAVIOR OF DIRECTIONAL TOOL, DECISION IS MADE; TO MAKE TRIP TO SURFACE TO CHANGE BHA #3.</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>428c3c1d3491586ae82554a8fcb3d480b6bd4cb53c3bfa2eeb058a58b29a9699</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11:operations:3</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>operations.operation_details</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>BOMBEA TÁNDEM DE PÍLDORAS, 80 BBL DE PÍLDORA DE BAJA REOLOGÍA / DISPERSA DE; 8.5–8.7 LPG x 27 SEG/QT SEGUIDO DE 80 BBL DE PÍLDORA VISCOSA PESADA DE 11.5 LPG x 120; SEG/QT,; CIRCULA HASTA OBTENER RETORNOS LIMPIOS EN ZARANDAS, OK; TOTAL STKS: 18550. TOMA PRESION REDUCIDA @ 10832'; BOMBA #1 BOMBA #2; 30 SPM 80 PSI 30 SPM. 280 PSI; 40 SPM. 310 PSI 40 SPM. 310 PSI; 50 SPM. 400 PSI 50 SPM. 400 PSI; REALIZA CHECK FLOW POR 5 MIN, OK.</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>PILLAR TANDEM PUMPING, 80 BBL OF LOW REOLOGY / DISPERSED PILLS; 8.5–8.7 LPG x 27 SEG/QT FOLLOWED BY 80 BBL OF HEAVY VISCOSITY PILLS AT 11.5 LPG x 120; SEG/QT, CIRCULATE UNTIL CLEAN RETURNS ARE OBTAINED IN SCREENS, OK; TOTAL STKS: 18550. TAKE REDUCED PRESSURE @ 10832'; PUMP #1 PUMP #2; 30 SPM 80 PSI 30 SPM. 280 PSI; 40 SPM. 310 PSI 40 SPM. 310 PSI; 50 SPM. 400 PSI 50 SPM. 400 PSI; PERFORM FLOW CHECK FOR 5 MIN, OK.</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>5f469c30482a006f0df147c002f75e55174b549112bd86446536e0ff38b71a37</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11:operations:4</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>operations.operation_details</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>SACA BHA# 03 EN HOYO ABIERTO, LLENANDO POZO DE FORMA CONTINUA CON TANQUE DE; VIAJE Y MONITOREANDO VOLUMEN DE LLENADO CON TANQUE DE VIAJE DESDE 10832 PIES; HASTA 7610 PIES (ZAPATO 13 3/8").. SACA EN ELEVADORES DESDE 10832' HASTA 8700'. SACA CON BACKREAMING DESDE 8700' HASTA 7610' (CONGL. INFERIOR Y SUPERIOR). CON 900-1050 GPM, 2200-2850 PSI, 40-60 RPM, 15-32 KLBS.PIE. MAXIMO OVERPULL 50 KLBS. NOTAS: *OBSERVA PARO DE ROTARIA DURANTE EL BACKREAMING. *INTENTA SACAR EN ELEVADORES DENTRO DEL REVESTIDOR 13 3/8" CON MAXIMO OVERPULL; 50 KLBS, SIN EXITO.</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>RETRACT BHA# 03 IN OPEN HOLE, CONTINUOUSLY FILLING WELL WITH TRIP TANK AND MONITORING VOLUME OF FILLED FROM TRIP TANK FROM 10832 FEET; UNTIL 7610 FEET (SHOE 13 3/8"). RETRACT IN DERRICKS FROM 10832' TO 8700'. RETRACT WITH BACKREAMING FROM 8700' TO 7610' (LOWER AND UPPER CONGLO.). WITH 900-1050 GPM, 2200-2850 PSI, 40-60 RPM, 15-32 KLBS.FT. MAXIMUM OVERPULL 50 KLBS. NOTES: *OBSERVE ROTARY STOP DURING BACKREAMING. *ATTEMPT TO PULL OUT IN DRAINS INSIDE THE 13 3/8" CASING WITH MAXIMUM OVERPULL; 50 KLBS, WITHOUT SUCCESS.</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>9834875e6ff3edbb5da2e32a0274822b5cb38871ca5bfbec1103995465c39d86</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11:operations:5</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>operations.operation_details</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>BOMBEA TREN DE PILDORAS CON 60 BLS DE PLIDRA DISPERSA DE 8.5 LPG x 27 SEG/QT; SEGUIDO DE 60 BLS DE PILDORA VISCOSA DE 9.8 LPG x 124 SEG/QT. CIRCULA HASTA; OBSERVAR PILDORAS EN SUPERFCIE CON 1050 GPM, 2750 PSI, 60 RPM, 18-22 KLBS-PIE. MAXIMO INCREMENTO DE SOLIDOS 5%. OBSERVA TROZOS DE GOMA EN ZARANDAS.</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>PUMP PILL TRAIN WITH 60 BLS OF DISPERSED PILLED DRUGS AT 8.5 LPG x 27 SEG/QT; FOLLOWED BY 60 BLS OF VISCOS PILLED DRUGS AT 9.8 LPG x 124 SEG/QT. CIRCULATES UNTIL; OBSERVE PILL ON SURFACE WITH 1050 GPM, 2750 PSI, 60 RPM, 18-22 KLBS-FEET. MAXIMUM SOLIDS INCREMENT 5%. OBSERVE RUBBER PIECES IN SIEVES.</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>8b3c957972a9062d397693251c58014cd501ca998cebeda866056903d3647d61</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11:operations:6</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>operations.operation_details</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>SACA BHA #3 EN HOYO ENTUBADO DESDE 7610 PIES HASTA 2000 PIES. NOTAS: *INTENTA SACAR EN ELEVADORES CON MAXIMO OVERPULL HASTA 50 KLBS, SIN EXITO; *SACA CON BOMBA CON 900 GPM, 2000 PSI DESDE 7610 PIES HASTA 6557 PIES; *BOMBEA 30 BLS DE PILDORA PESADA DE 12.0 LPG; *SACA LIBRE EN ELEVADORES DESDE 6557 PIES. *UTILIZA LLAVES DE FUERZA EN ALGUNAS CONEXIONES CON SOBRETORQUE; Incident Comments:</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>RETRACT BHA #3 FROM Cased Hole FROM 7610 FEET TO 2000 FEET. NOTES: *ATTEMPTED RETRACT WITH MAXIMUM OVERPULL UP TO 50 KLBS, WITHOUT SUCCESS; *RETRACT WITH PUMP AT 900 GPM, 2000 PSI FROM 7610 FEET TO 6557 FEET; *PUMPS 30 BLS OF HEAVY PILL 12.0 LPG; *FREE RETRACT IN DRILLS FROM 6557 FEET. *USE TORQUE WRENCHES ON SOME CONNECTIONS WITH OVER-TORQUING; Incident Comments:</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>bfcb3bafbaae8357e3744cbb26c3fe282b0922a077fc4a24be6664853a41d1f1</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:29:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>daily_report</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>report_fields.currentOps</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>SACANDO BHA #3 DIRECCIONAL CON ICRUISE, MWD Y BROCA PDC 12 1/4" EN HOYO ENTUBADO @ 1700 PIES</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>SACANDO BHA #3 DIRECCIONAL CON ICRUISE, MWD Y BROCA PDC 12 1/4" EN HOYO ENTUBADO @ 1700 PIES</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>3d04f5fdeb1cb643192e621d1c1d365e64d1cdc594c3bf777f05a1867c733f55</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>NOT_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>daily_report</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>report_fields.forecast24h</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>SACAR BHA #3 HASTA SUPERFICIE. QUEBRAR HTAS. DIRECCIONALES Y BROCA. ARMAR Y BAJAR BHA #4 DIRECCIONAL CON ICRUISE, MWD Y BROCA PDC 12 1/4" HASTA EL FONDO @ 10832' REFRESCAR FLUIDO Y LUBRICIDAD AL 2%. DENSIFICAR A 10.5 LPG PERFORAR CON BHA #4 SECCION 12 1/4"</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>SACAR BHA #3 HASTA SUPERFICIE. QUEBRAR HTAS. DIRECCIONALES Y BROCA. ARMAR Y BAJAR BHA #4 DIRECCIONAL CON ICRUISE, MWD Y BROCA PDC 12 1/4" HASTA EL FONDO @ 10832' REFRESCAR FLUIDO Y LUBRICIDAD AL 2%. DENSIFICAR A 10.5 LPG PERFORAR CON BHA #4 SECCION 12 1/4"</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>c2d4196e428a63bbf5b0f12ef93d7409278d508f3ef659f40718a12b2f641438</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>NOT_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>daily_report</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>report_fields.incidentComments</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Environ Incident? N Days since Last LTA 188.00INCIDENTES SIN REPORTAR EN LAS ULTIMAS 24 HORAS.</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Environ Incident? N Days since Last LTA 188.00INCIDENTES SIN REPORTAR EN LAS ULTIMAS 24 HORAS.</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>320fb51cfe6f7b2054d4d4b5eede085f7ecaf164f93a428ad2438f63eecf7524</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>NOT_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>daily_report</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>report_fields.mudComments</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Durante perforación de formacion Tena bombea píldoras</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Durante perforación de formacion Tena bombea píldoras</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>05683f18e40e86bf9ce56a656b25ad3ceea4130c99d4ebe8ba70ad885ed3ef98</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>NOT_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>daily_report</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>report_fields.otherRemarks</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>POB: MINICAMP 30 PAX CAMPAMENTO 47 PAX -(1) VACUUM (178 BBL): TRASLADO DE FLUIDOS DE AGUA TRATADA DE BSS Y AGUAS GRISES DE CAMPAMENTOS. -(1) VACUUM (130 BBL): TRASLADO DE FLUIDO CONTAMINADOS SNP -248 -PERSONAL APROBADO PARA CAPATAZ DE PERSONAL COMUNITARIO (OBREROS DE PATIO ), ESTE SERVICIO SE BRINDA DESDE EL 22 DE ENERO DE 2026. -SERVICIO DE RIGGER PARA MONTACARGA DESDE EL DIA 27 DE MARZO DEL 2026 -INGRESA DESDE EL 8 DE MAYO 2026 BUSETA PROVISTA POR HALLIBURTON PARA MOVILIZACION DE PERSONAL -INGRESA DESDE EL 8 DE MAYO 2026 CAMA ALTA PROVISTA POR HALLIBURTON PARA MOVILIZAR CARGAS DESDE PUCUNA 6 A PUCUNA C -INGRESA DESDE EL 8 DE MAYO 2026 MONTACARGAS DE 10 TON PROVISTA POR HALLIBURTON PARA CARGAS EN PUCUNA 6 (OPERADOR +RIGGER)+ INGRESA DESDE EL 14 DE MAYO UN OPERADOR DE MONTACARGAS PARA TRABAJO EN LA NOCHE HASTA EL LUNES 18 DE MAYO -PERSONAL DE GLOBAL INSPECCION SE RETIRA DE LOCACION -PERSONAL DE MISSION PETROLEUM INSTALA ANILLOS DE TORQUE 9 5/8IN FECHA DE INGRESO 9 DE JUNIO 2026 -INGRESA PERSONAL DE SINOPEC TUBULARES PARA COORDINAR EL ORDEN DE LA TUBERIA DE LOS RACKS. -INGRESA CEMENTO TIPO A 887 SACOS REPORTE DIARIO *EVACUACIONES DE CORTES DE PERFORACIÓN. TOTAL VOLUMEN DIARIO EVACUADO CORTES NORMALES DE PERFORACIÓN : 80.00 M3 TOTAL VOLUMEN DIARIO EVACUADO CORTES CON CEMENTO = 00.00 M3 N° VIAJES DIARIO = 8 VOLUMEN ACUMULADO CORTES NORMALES = 1855.50 M3 VOLUMEN ACUMULADO CORTES CON CEMENTO = 86.00 M3 TOTAL VIAJES ACUMULADO = 200</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>POB: MINICAMP 30 PAX CAMPAMENTO 47 PAX -(1) VACUUM (178 BBL): TRASLADO DE FLUIDOS DE AGUA TRATADA DE BSS Y AGUAS GRISES DE CAMPAMENTOS. -(1) VACUUM (130 BBL): TRASLADO DE FLUIDO CONTAMINADOS SNP -248 -PERSONAL APROBADO PARA CAPATAZ DE PERSONAL COMUNITARIO (OBREROS DE PATIO ), ESTE SERVICIO SE BRINDA DESDE EL 22 DE ENERO DE 2026. -SERVICIO DE RIGGER PARA MONTACARGA DESDE EL DIA 27 DE MARZO DEL 2026 -INGRESA DESDE EL 8 DE MAYO 2026 BUSETA PROVISTA POR HALLIBURTON PARA MOVILIZACION DE PERSONAL -INGRESA DESDE EL 8 DE MAYO 2026 CAMA ALTA PROVISTA POR HALLIBURTON PARA MOVILIZAR CARGAS DESDE PUCUNA 6 A PUCUNA C -INGRESA DESDE EL 8 DE MAYO 2026 MONTACARGAS DE 10 TON PROVISTA POR HALLIBURTON PARA CARGAS EN PUCUNA 6 (OPERADOR +RIGGER)+ INGRESA DESDE EL 14 DE MAYO UN OPERADOR DE MONTACARGAS PARA TRABAJO EN LA NOCHE HASTA EL LUNES 18 DE MAYO -PERSONAL DE GLOBAL INSPECCION SE RETIRA DE LOCACION -PERSONAL DE MISSION PETROLEUM INSTALA ANILLOS DE TORQUE 9 5/8IN FECHA DE INGRESO 9 DE JUNIO 2026 -INGRESA PERSONAL DE SINOPEC TUBULARES PARA COORDINAR EL ORDEN DE LA TUBERIA DE LOS RACKS. -INGRESA CEMENTO TIPO A 887 SACOS REPORTE DIARIO *EVACUACIONES DE CORTES DE PERFORACIÓN. TOTAL VOLUMEN DIARIO EVACUADO CORTES NORMALES DE PERFORACIÓN : 80.00 M3 TOTAL VOLUMEN DIARIO EVACUADO CORTES CON CEMENTO = 00.00 M3 N° VIAJES DIARIO = 8 VOLUMEN ACUMULADO CORTES NORMALES = 1855.50 M3 VOLUMEN ACUMULADO CORTES CON CEMENTO = 86.00 M3 TOTAL VIAJES ACUMULADO = 200</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>d68721850a25c8aa7aae985a9d565792ac06619d73b047f34a0c312ca7edcc98</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>NOT_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>daily_report</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>report_fields.summary24h</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>PERFORÓ CON BHA #3 DIRECCIONAL CON ICRUISE, MWD Y BROCA PDC 12 1/4" DESDE 10641 PIES HASTA 10832 PIES. BOMBEÓ TREN DE PILDORAS Y CIRCULÓ HASTA RETORNOS LIMPIOS. SACA BHA #3 EN VIAJE A SUPERFICIE PARA CAMBIO DE BHA DESDE 10832 PIES HASTA 1700 PIES</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>PERFORÓ CON BHA #3 DIRECCIONAL CON ICRUISE, MWD Y BROCA PDC 12 1/4" DESDE 10641 PIES HASTA 10832 PIES. BOMBEÓ TREN DE PILDORAS Y CIRCULÓ HASTA RETORNOS LIMPIOS. SACA BHA #3 EN VIAJE A SUPERFICIE PARA CAMBIO DE BHA DESDE 10832 PIES HASTA 1700 PIES</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>01a5b24ac0169764755fa891eb5d68079b9cd31ef1f37f9a9814c19130eb9b38</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>NOT_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11:operations:1</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>operations.operation_details</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>PERFORA CON BHA #3 DIRECCIONAL CON iCRUISE, MWD Y BROCA PDC 12 1/4" ATRAVESANDO; FORMACIÓN TENA DESDE 10641 PIES HASTA 10832 PIES. PARÁMETROS: 1000 GPM, 2800 PSI, 120 RPM, TQ 25–28 KLBS-PIE, WOB 40–50 KLBS. AVANCE: 191 PIES, ROP PROMEDIO: 32 PPH. REALIZA DOS REPASOS CADA PARADA; BOMBEA 60 BBL DE PÍLDORA DE BAJA REOLOGÍA / DISPERSA DE 8.5 LPG x 27 SEG/QT @ 10656'; Y 10755'. ULTIMO SURVEY; 10718' MD / 8442.2' TVD, INC: 43.16°, AZI: 13.07°, CT-CT: 13.1', 10.4' ARRIBA, 8' DERECHA; ULTIMA MUESTRA (TENA) @ 10832'; 100% ARCILLOLITA; BROCA: ROTADOS: 191 PIES, 4.48 HORAS, ROP NETO: 42.63 PPH, 100%; PESO DE SARTA: ARRIBA 430 KLBS, ROTANDO 275 KLBS, ABAJO 190 KLBS. TÉCNICO DE WWT INSTALA REDUCTORES DE TORQUE DESDE PARADA #53 HASTA PARADA #96. TOTAL INSTALADOS: 129/150 UNIDADES.</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>PERFORA CON BHA #3 DIRECCIONAL CON iCRUISE, MWD Y BROCA PDC 12 1/4" ATRAVESANDO; FORMACIÓN TENA DESDE 10641 PIES HASTA 10832 PIES. PARÁMETROS: 1000 GPM, 2800 PSI, 120 RPM, TQ 25–28 KLBS-PIE, WOB 40–50 KLBS. AVANCE: 191 PIES, ROP PROMEDIO: 32 PPH. REALIZA DOS REPASOS CADA PARADA; BOMBEA 60 BBL DE PÍLDORA DE BAJA REOLOGÍA / DISPERSA DE 8.5 LPG x 27 SEG/QT @ 10656'; Y 10755'. ULTIMO SURVEY; 10718' MD / 8442.2' TVD, INC: 43.16°, AZI: 13.07°, CT-CT: 13.1', 10.4' ARRIBA, 8' DERECHA; ULTIMA MUESTRA (TENA) @ 10832'; 100% ARCILLOLITA; BROCA: ROTADOS: 191 PIES, 4.48 HORAS, ROP NETO: 42.63 PPH, 100%; PESO DE SARTA: ARRIBA 430 KLBS, ROTANDO 275 KLBS, ABAJO 190 KLBS. TÉCNICO DE WWT INSTALA REDUCTORES DE TORQUE DESDE PARADA #53 HASTA PARADA #96. TOTAL INSTALADOS: 129/150 UNIDADES.</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>2cf1da753a81ab0834976eca34077332d8f1fb58036d9f2d57264e6fd820248f</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>NOT_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11:operations:2</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>operations.operation_details</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>HALLIBURTON SPERRY REALIZA RESETEO DE HERRAMIENTAS DIRECCIONALES Y ENVÍA; DOWNLINK PARA iCRUISE,; **NOTA**; DEBIDO A FALLA / COMPORTAMIENTO ANÓMALO DE HERRAMIENTA DIRECCIONAL, SE DECIDE; REALIZAR VIAJE A SUPERFICIE PARA CAMBIO DE BHA #3.</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>HALLIBURTON SPERRY REALIZA RESETEO DE HERRAMIENTAS DIRECCIONALES Y ENVÍA; DOWNLINK PARA iCRUISE,; **NOTA**; DEBIDO A FALLA / COMPORTAMIENTO ANÓMALO DE HERRAMIENTA DIRECCIONAL, SE DECIDE; REALIZAR VIAJE A SUPERFICIE PARA CAMBIO DE BHA #3.</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>428c3c1d3491586ae82554a8fcb3d480b6bd4cb53c3bfa2eeb058a58b29a9699</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>NOT_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11:operations:3</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>operations.operation_details</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>BOMBEA TÁNDEM DE PÍLDORAS, 80 BBL DE PÍLDORA DE BAJA REOLOGÍA / DISPERSA DE; 8.5–8.7 LPG x 27 SEG/QT SEGUIDO DE 80 BBL DE PÍLDORA VISCOSA PESADA DE 11.5 LPG x 120; SEG/QT,; CIRCULA HASTA OBTENER RETORNOS LIMPIOS EN ZARANDAS, OK; TOTAL STKS: 18550. TOMA PRESION REDUCIDA @ 10832'; BOMBA #1 BOMBA #2; 30 SPM 80 PSI 30 SPM. 280 PSI; 40 SPM. 310 PSI 40 SPM. 310 PSI; 50 SPM. 400 PSI 50 SPM. 400 PSI; REALIZA CHECK FLOW POR 5 MIN, OK.</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>BOMBEA TÁNDEM DE PÍLDORAS, 80 BBL DE PÍLDORA DE BAJA REOLOGÍA / DISPERSA DE; 8.5–8.7 LPG x 27 SEG/QT SEGUIDO DE 80 BBL DE PÍLDORA VISCOSA PESADA DE 11.5 LPG x 120; SEG/QT,; CIRCULA HASTA OBTENER RETORNOS LIMPIOS EN ZARANDAS, OK; TOTAL STKS: 18550. TOMA PRESION REDUCIDA @ 10832'; BOMBA #1 BOMBA #2; 30 SPM 80 PSI 30 SPM. 280 PSI; 40 SPM. 310 PSI 40 SPM. 310 PSI; 50 SPM. 400 PSI 50 SPM. 400 PSI; REALIZA CHECK FLOW POR 5 MIN, OK.</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>5f469c30482a006f0df147c002f75e55174b549112bd86446536e0ff38b71a37</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>NOT_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11:operations:4</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>operations.operation_details</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>SACA BHA# 03 EN HOYO ABIERTO, LLENANDO POZO DE FORMA CONTINUA CON TANQUE DE; VIAJE Y MONITOREANDO VOLUMEN DE LLENADO CON TANQUE DE VIAJE DESDE 10832 PIES; HASTA 7610 PIES (ZAPATO 13 3/8").. SACA EN ELEVADORES DESDE 10832' HASTA 8700'. SACA CON BACKREAMING DESDE 8700' HASTA 7610' (CONGL. INFERIOR Y SUPERIOR). CON 900-1050 GPM, 2200-2850 PSI, 40-60 RPM, 15-32 KLBS.PIE. MAXIMO OVERPULL 50 KLBS. NOTAS: *OBSERVA PARO DE ROTARIA DURANTE EL BACKREAMING. *INTENTA SACAR EN ELEVADORES DENTRO DEL REVESTIDOR 13 3/8" CON MAXIMO OVERPULL; 50 KLBS, SIN EXITO.</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>SACA BHA# 03 EN HOYO ABIERTO, LLENANDO POZO DE FORMA CONTINUA CON TANQUE DE; VIAJE Y MONITOREANDO VOLUMEN DE LLENADO CON TANQUE DE VIAJE DESDE 10832 PIES; HASTA 7610 PIES (ZAPATO 13 3/8").. SACA EN ELEVADORES DESDE 10832' HASTA 8700'. SACA CON BACKREAMING DESDE 8700' HASTA 7610' (CONGL. INFERIOR Y SUPERIOR). CON 900-1050 GPM, 2200-2850 PSI, 40-60 RPM, 15-32 KLBS.PIE. MAXIMO OVERPULL 50 KLBS. NOTAS: *OBSERVA PARO DE ROTARIA DURANTE EL BACKREAMING. *INTENTA SACAR EN ELEVADORES DENTRO DEL REVESTIDOR 13 3/8" CON MAXIMO OVERPULL; 50 KLBS, SIN EXITO.</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>9834875e6ff3edbb5da2e32a0274822b5cb38871ca5bfbec1103995465c39d86</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>NOT_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11:operations:5</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>operations.operation_details</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>BOMBEA TREN DE PILDORAS CON 60 BLS DE PLIDRA DISPERSA DE 8.5 LPG x 27 SEG/QT; SEGUIDO DE 60 BLS DE PILDORA VISCOSA DE 9.8 LPG x 124 SEG/QT. CIRCULA HASTA; OBSERVAR PILDORAS EN SUPERFCIE CON 1050 GPM, 2750 PSI, 60 RPM, 18-22 KLBS-PIE. MAXIMO INCREMENTO DE SOLIDOS 5%. OBSERVA TROZOS DE GOMA EN ZARANDAS.</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>BOMBEA TREN DE PILDORAS CON 60 BLS DE PLIDRA DISPERSA DE 8.5 LPG x 27 SEG/QT; SEGUIDO DE 60 BLS DE PILDORA VISCOSA DE 9.8 LPG x 124 SEG/QT. CIRCULA HASTA; OBSERVAR PILDORAS EN SUPERFCIE CON 1050 GPM, 2750 PSI, 60 RPM, 18-22 KLBS-PIE. MAXIMO INCREMENTO DE SOLIDOS 5%. OBSERVA TROZOS DE GOMA EN ZARANDAS.</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>8b3c957972a9062d397693251c58014cd501ca998cebeda866056903d3647d61</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>NOT_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>drilling:PCNC-040:2026-06-11:11:operations:6</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>operations.operation_details</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>SACA BHA #3 EN HOYO ENTUBADO DESDE 7610 PIES HASTA 2000 PIES. NOTAS: *INTENTA SACAR EN ELEVADORES CON MAXIMO OVERPULL HASTA 50 KLBS, SIN EXITO; *SACA CON BOMBA CON 900 GPM, 2000 PSI DESDE 7610 PIES HASTA 6557 PIES; *BOMBEA 30 BLS DE PILDORA PESADA DE 12.0 LPG; *SACA LIBRE EN ELEVADORES DESDE 6557 PIES. *UTILIZA LLAVES DE FUERZA EN ALGUNAS CONEXIONES CON SOBRETORQUE; Incident Comments:</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>SACA BHA #3 EN HOYO ENTUBADO DESDE 7610 PIES HASTA 2000 PIES. NOTAS: *INTENTA SACAR EN ELEVADORES CON MAXIMO OVERPULL HASTA 50 KLBS, SIN EXITO; *SACA CON BOMBA CON 900 GPM, 2000 PSI DESDE 7610 PIES HASTA 6557 PIES; *BOMBEA 30 BLS DE PILDORA PESADA DE 12.0 LPG; *SACA LIBRE EN ELEVADORES DESDE 6557 PIES. *UTILIZA LLAVES DE FUERZA EN ALGUNAS CONEXIONES CON SOBRETORQUE; Incident Comments:</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>bfcb3bafbaae8357e3744cbb26c3fe282b0922a077fc4a24be6664853a41d1f1</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>drilling-daily-v4</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>NOT_REQUIRED</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:33:32+00:00</t>
         </is>
       </c>
     </row>

--- a/outputs/report_database.xlsx
+++ b/outputs/report_database.xlsx
@@ -2341,12 +2341,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2026-07-10T15:46:43+00:00</t>
+          <t>2026-07-10T15:47:04+00:00</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
